--- a/results/regression_output/pre_covid_analysis/price_robustness_matrix.xlsx
+++ b/results/regression_output/pre_covid_analysis/price_robustness_matrix.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,87 +417,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>spec_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>control_spec</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>price_measure</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price_description</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>n_controls</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>eu_elasticity</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>eu_se</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>eu_pval</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>eap_elasticity</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>eap_se</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>eap_pval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>interaction_coef</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>interaction_pval</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>r_squared</t>
         </is>
@@ -543,28 +531,28 @@
         <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1154315327473595</v>
+        <v>-0.1012746800182214</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05483296800165784</v>
+        <v>0.05275385897832816</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03618212557027589</v>
+        <v>0.05591911331221899</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.6091572353765753</v>
+        <v>-0.5950760110920712</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07711514409552492</v>
+        <v>0.07595852059371849</v>
       </c>
       <c r="L2" t="n">
-        <v>6.683542608243442e-14</v>
+        <v>1.023625628704394e-13</v>
       </c>
       <c r="M2" t="n">
-        <v>5.277216899734095</v>
+        <v>5.875861676235409</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4937257026292158</v>
+        <v>-0.4938013310738498</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -573,7 +561,7 @@
         <v>330</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4077433673083014</v>
+        <v>0.403069015694194</v>
       </c>
     </row>
     <row r="3">
@@ -604,37 +592,37 @@
         <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1158825156151602</v>
+        <v>-0.1013087820410415</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05543155839011415</v>
+        <v>0.05423975866894883</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0374667862375635</v>
+        <v>0.06283138137427047</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.5869033239689503</v>
+        <v>-0.5701733674122083</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0873322900666722</v>
+        <v>0.08462373399190269</v>
       </c>
       <c r="L3" t="n">
-        <v>1.007165462141302e-10</v>
+        <v>9.086242869216221e-11</v>
       </c>
       <c r="M3" t="n">
-        <v>5.064640863665971</v>
+        <v>5.628074446509719</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4710208083537901</v>
+        <v>-0.4688645853711668</v>
       </c>
       <c r="O3" t="n">
-        <v>2.131939069727196e-11</v>
+        <v>4.932942943014496e-12</v>
       </c>
       <c r="P3" t="n">
         <v>330</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3687322681732338</v>
+        <v>0.3637789415331618</v>
       </c>
     </row>
     <row r="4">
@@ -665,28 +653,28 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1649218012390685</v>
+        <v>-0.1422961552191508</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04150671860181034</v>
+        <v>0.04164735291690167</v>
       </c>
       <c r="I4" t="n">
-        <v>8.998202282950452e-05</v>
+        <v>0.0007268483647278057</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6291249223600274</v>
+        <v>-0.6184671711737429</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06165217011677911</v>
+        <v>0.06144700679653801</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.814686218761679</v>
+        <v>4.346337891007943</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4642031211209589</v>
+        <v>-0.4761710159545921</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -695,7 +683,7 @@
         <v>330</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3515984955856093</v>
+        <v>0.3369701883695086</v>
       </c>
     </row>
     <row r="5">
@@ -726,37 +714,37 @@
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.08907357686081817</v>
+        <v>-0.08958684331528761</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04334966613875779</v>
+        <v>0.04336494073981145</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04081596912934504</v>
+        <v>0.03974645259266163</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6042160088263714</v>
+        <v>-0.6038543099674142</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08650774548644204</v>
+        <v>0.08660433020564759</v>
       </c>
       <c r="L5" t="n">
-        <v>2.030531298657934e-11</v>
+        <v>2.18360884929325e-11</v>
       </c>
       <c r="M5" t="n">
-        <v>6.783336092705568</v>
+        <v>6.740435175757209</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5151424319655532</v>
+        <v>-0.5142674666521265</v>
       </c>
       <c r="O5" t="n">
-        <v>3.793498848381205e-11</v>
+        <v>4.30653290806049e-11</v>
       </c>
       <c r="P5" t="n">
         <v>330</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2778786084066538</v>
+        <v>0.2774644207172029</v>
       </c>
     </row>
     <row r="6">
@@ -787,37 +775,37 @@
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.03256979643026289</v>
+        <v>-0.03323752408890467</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07450538763465613</v>
+        <v>0.07440104400984482</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6623382286701092</v>
+        <v>0.655408332119124</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5964395374090085</v>
+        <v>-0.5960227390393019</v>
       </c>
       <c r="K6" t="n">
-        <v>0.116572086080338</v>
+        <v>0.1165329424726069</v>
       </c>
       <c r="L6" t="n">
-        <v>5.7520500829078e-07</v>
+        <v>5.804106248952223e-07</v>
       </c>
       <c r="M6" t="n">
-        <v>18.31265782351696</v>
+        <v>17.93222435717665</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5638697409787455</v>
+        <v>-0.5627852149503972</v>
       </c>
       <c r="O6" t="n">
-        <v>1.205781474666878e-09</v>
+        <v>1.309377495317676e-09</v>
       </c>
       <c r="P6" t="n">
         <v>330</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.29600268868056</v>
+        <v>0.2955499435836599</v>
       </c>
     </row>
     <row r="7">
@@ -848,28 +836,28 @@
         <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1398502643201729</v>
+        <v>-0.1042039704432872</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02814002330474057</v>
+        <v>0.027955789074258</v>
       </c>
       <c r="I7" t="n">
-        <v>1.164555711419268e-06</v>
+        <v>0.0002337105161123176</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6358142906140419</v>
+        <v>-0.6214122143746015</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05900787281843666</v>
+        <v>0.0593553884283942</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>4.546393199217771</v>
+        <v>5.96342165976107</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.495964026293869</v>
+        <v>-0.5172082439313143</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -878,7 +866,7 @@
         <v>330</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2983535096610027</v>
+        <v>0.2770951802582408</v>
       </c>
     </row>
     <row r="8">
@@ -909,28 +897,28 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0936415282249617</v>
+        <v>-0.09423942220541649</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03971181078050009</v>
+        <v>0.03982449669822309</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01905272688766191</v>
+        <v>0.01863714556317131</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6312092142183778</v>
+        <v>-0.6308449359973219</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06549614167284182</v>
+        <v>0.0656358092886765</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6.740697489493967</v>
+        <v>6.694066254165378</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5375676859934161</v>
+        <v>-0.5366055137919055</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -939,7 +927,7 @@
         <v>330</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3012598309583548</v>
+        <v>0.3009180083040703</v>
       </c>
     </row>
     <row r="9">
@@ -970,37 +958,37 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.08139397123409917</v>
+        <v>-0.08194043458782239</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04169927565867901</v>
+        <v>0.04169188303671995</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05192596311908515</v>
+        <v>0.05034106042070841</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6154347561486616</v>
+        <v>-0.6150393409074353</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08612396986985485</v>
+        <v>0.08619240858568283</v>
       </c>
       <c r="L9" t="n">
-        <v>7.506661958700533e-12</v>
+        <v>7.997380535584853e-12</v>
       </c>
       <c r="M9" t="n">
-        <v>7.561183547348917</v>
+        <v>7.505932132300889</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5340407849145624</v>
+        <v>-0.5330989063196129</v>
       </c>
       <c r="O9" t="n">
-        <v>1.079492051303532e-11</v>
+        <v>1.222000278744417e-11</v>
       </c>
       <c r="P9" t="n">
         <v>330</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.274471895349625</v>
+        <v>0.2740896489927416</v>
       </c>
     </row>
     <row r="10">
@@ -1031,37 +1019,37 @@
         <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.08752192806254232</v>
+        <v>-0.08692922632801429</v>
       </c>
       <c r="H10" t="n">
-        <v>0.05267440328155256</v>
+        <v>0.05176555333203501</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09773547608216737</v>
+        <v>0.09422773787071947</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2033945781130005</v>
+        <v>-0.201125537531641</v>
       </c>
       <c r="K10" t="n">
-        <v>0.118983622158823</v>
+        <v>0.1190180056772252</v>
       </c>
       <c r="L10" t="n">
-        <v>0.08849469146068456</v>
+        <v>0.09218102626198599</v>
       </c>
       <c r="M10" t="n">
-        <v>2.323927073083407</v>
+        <v>2.313669936192969</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1158726500504582</v>
+        <v>-0.1141963112036267</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2783911326332453</v>
+        <v>0.2875570881731864</v>
       </c>
       <c r="P10" t="n">
         <v>330</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2250405812373095</v>
+        <v>0.2249862438760502</v>
       </c>
     </row>
     <row r="11">
@@ -1092,37 +1080,37 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.09022926138595622</v>
+        <v>-0.0917613636469798</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05405967800019972</v>
+        <v>0.05483596462568301</v>
       </c>
       <c r="I11" t="n">
-        <v>0.096217663291569</v>
+        <v>0.09536545944656161</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2127391151079198</v>
+        <v>-0.2112470180884315</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1072378640230745</v>
+        <v>0.1060068296409136</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04825042045937167</v>
+        <v>0.04725394141242312</v>
       </c>
       <c r="M11" t="n">
-        <v>2.357761903845438</v>
+        <v>2.302134686022447</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1225098537219636</v>
+        <v>-0.1194856544414517</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1869812247327991</v>
+        <v>0.1888935318763147</v>
       </c>
       <c r="P11" t="n">
         <v>330</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1881243568225742</v>
+        <v>0.1905718733684744</v>
       </c>
     </row>
     <row r="12">
@@ -1153,37 +1141,37 @@
         <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1299040133800803</v>
+        <v>-0.1250952518091577</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06192478648695685</v>
+        <v>0.06298787625571635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03681218292412303</v>
+        <v>0.04799560882284459</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2500817453853373</v>
+        <v>-0.2444837981111417</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09635144999840545</v>
+        <v>0.09612199239963096</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00993763055010799</v>
+        <v>0.01150786283431304</v>
       </c>
       <c r="M12" t="n">
-        <v>1.92512716796235</v>
+        <v>1.954381118190802</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.120177732005257</v>
+        <v>-0.1193885463019839</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1046262688331967</v>
+        <v>0.1012282346155615</v>
       </c>
       <c r="P12" t="n">
         <v>330</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1377546100622007</v>
+        <v>0.1285444921606054</v>
       </c>
     </row>
     <row r="13">
@@ -1214,37 +1202,37 @@
         <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1155926840307243</v>
+        <v>-0.1156392715294208</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05190056956699413</v>
+        <v>0.05199697038552986</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02671806592934733</v>
+        <v>0.02693741360588309</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1639826312708945</v>
+        <v>-0.1637673583693385</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1095750682167152</v>
+        <v>0.1096521600333624</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1356254632030267</v>
+        <v>0.1364120607850898</v>
       </c>
       <c r="M13" t="n">
-        <v>1.418624652986761</v>
+        <v>1.41619154291951</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04838994724017019</v>
+        <v>-0.04812808683991776</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6164574621086061</v>
+        <v>0.6184952653703819</v>
       </c>
       <c r="P13" t="n">
         <v>330</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07112716183102819</v>
+        <v>0.0708976237478558</v>
       </c>
     </row>
     <row r="14">
@@ -1275,37 +1263,37 @@
         <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.08099468784241948</v>
+        <v>-0.0810737207880399</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05005207789609519</v>
+        <v>0.05012036575072828</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1067316616191156</v>
+        <v>0.1068670762887582</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1547330257057855</v>
+        <v>-0.1545044948142994</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1177441296200725</v>
+        <v>0.1177796018541008</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1898611045609522</v>
+        <v>0.1906472892557163</v>
       </c>
       <c r="M14" t="n">
-        <v>1.910409556819687</v>
+        <v>1.905728432252884</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.07373833786336596</v>
+        <v>-0.07343077402625947</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4895772762318171</v>
+        <v>0.4914176218672703</v>
       </c>
       <c r="P14" t="n">
         <v>330</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.09120458661219022</v>
+        <v>0.09100306375979428</v>
       </c>
     </row>
     <row r="15">
@@ -1336,37 +1324,37 @@
         <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.130891592930028</v>
+        <v>-0.1225762635233804</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06204129205356383</v>
+        <v>0.0629114735920958</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03576093469528474</v>
+        <v>0.05235974568974289</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1929461547172283</v>
+        <v>-0.1796818489793458</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1041095067123984</v>
+        <v>0.1017675759472893</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06488376873886215</v>
+        <v>0.07854343140638864</v>
       </c>
       <c r="M15" t="n">
-        <v>1.474091272006854</v>
+        <v>1.465878007817337</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06205456178720035</v>
+        <v>-0.05710558545596534</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4585585716386857</v>
+        <v>0.4758871617488782</v>
       </c>
       <c r="P15" t="n">
         <v>330</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.07411836574439257</v>
+        <v>0.05880099894762103</v>
       </c>
     </row>
     <row r="16">
@@ -1397,37 +1385,37 @@
         <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1038050976589836</v>
+        <v>-0.1038478372139866</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04795853189528317</v>
+        <v>0.04804047714267683</v>
       </c>
       <c r="I16" t="n">
-        <v>0.03126395949420702</v>
+        <v>0.03148164330347081</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1677544492657495</v>
+        <v>-0.167551056442428</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1243364345175555</v>
+        <v>0.1243667158363113</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1783518742978161</v>
+        <v>0.1789826141686581</v>
       </c>
       <c r="M16" t="n">
-        <v>1.616052130858253</v>
+        <v>1.613428463581538</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.06394935160676588</v>
+        <v>-0.06370321922844144</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5776518432126858</v>
+        <v>0.5791114822577139</v>
       </c>
       <c r="P16" t="n">
         <v>330</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.08127258602816079</v>
+        <v>0.08114530466849679</v>
       </c>
     </row>
     <row r="17">
@@ -1458,37 +1446,37 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1118309621422213</v>
+        <v>-0.1119279697906427</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05131859284183121</v>
+        <v>0.05143616243650622</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0301393273215298</v>
+        <v>0.03037235359795543</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1776544736824257</v>
+        <v>-0.1774597409034677</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1068103861041596</v>
+        <v>0.1068376800558504</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09735768653104437</v>
+        <v>0.09780866572558899</v>
       </c>
       <c r="M17" t="n">
-        <v>1.588598276177694</v>
+        <v>1.585481638194635</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0658235115402044</v>
+        <v>-0.06553177111282506</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4828253707029901</v>
+        <v>0.4846103881184072</v>
       </c>
       <c r="P17" t="n">
         <v>330</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.05415920248125761</v>
+        <v>0.05400941519282243</v>
       </c>
     </row>
     <row r="18">
@@ -1519,37 +1507,37 @@
         <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.09994662996236596</v>
+        <v>-0.09760414605409749</v>
       </c>
       <c r="H18" t="n">
-        <v>0.03990863353950008</v>
+        <v>0.0392888384780989</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01284346641998213</v>
+        <v>0.01357500325497729</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3457797153363183</v>
+        <v>-0.3396844116817059</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06835130414883112</v>
+        <v>0.06702015540221941</v>
       </c>
       <c r="L18" t="n">
-        <v>7.705188131978957e-07</v>
+        <v>7.360549447721354e-07</v>
       </c>
       <c r="M18" t="n">
-        <v>3.459643566436594</v>
+        <v>3.480225230324073</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2458330853739524</v>
+        <v>-0.2420802656276084</v>
       </c>
       <c r="O18" t="n">
-        <v>1.358913840476816e-05</v>
+        <v>1.20175347064766e-05</v>
       </c>
       <c r="P18" t="n">
         <v>330</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.2935206485426061</v>
+        <v>0.2921014599829125</v>
       </c>
     </row>
     <row r="19">
@@ -1580,37 +1568,37 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.09942209480475801</v>
+        <v>-0.09851930837513358</v>
       </c>
       <c r="H19" t="n">
-        <v>0.03818490196934671</v>
+        <v>0.03888190422776432</v>
       </c>
       <c r="I19" t="n">
-        <v>0.009712434226631705</v>
+        <v>0.01182661732315138</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3475224659648243</v>
+        <v>-0.3374395463820286</v>
       </c>
       <c r="K19" t="n">
-        <v>0.06199412533275744</v>
+        <v>0.06013286971239342</v>
       </c>
       <c r="L19" t="n">
-        <v>4.951789245311033e-08</v>
+        <v>4.803991071611335e-08</v>
       </c>
       <c r="M19" t="n">
-        <v>3.495424901751246</v>
+        <v>3.425110792466736</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2481003711600663</v>
+        <v>-0.238920238006895</v>
       </c>
       <c r="O19" t="n">
-        <v>6.888700849749796e-07</v>
+        <v>3.686257941115656e-07</v>
       </c>
       <c r="P19" t="n">
         <v>330</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.2584764060752283</v>
+        <v>0.2579319977482214</v>
       </c>
     </row>
     <row r="20">
@@ -1641,37 +1629,37 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1296653490442114</v>
+        <v>-0.1238992886599822</v>
       </c>
       <c r="H20" t="n">
-        <v>0.03853813969409283</v>
+        <v>0.04171140838987693</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0008724347481792183</v>
+        <v>0.00322925609872482</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3952665762683069</v>
+        <v>-0.3899023745975941</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05569605686097249</v>
+        <v>0.05606709710336186</v>
       </c>
       <c r="L20" t="n">
-        <v>1.029021312604073e-11</v>
+        <v>2.455791126010354e-11</v>
       </c>
       <c r="M20" t="n">
-        <v>3.048359327930661</v>
+        <v>3.146929888093275</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2656012272240955</v>
+        <v>-0.2660030859376119</v>
       </c>
       <c r="O20" t="n">
-        <v>1.959881146262887e-10</v>
+        <v>1.009858863199042e-11</v>
       </c>
       <c r="P20" t="n">
         <v>330</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2372289396324242</v>
+        <v>0.2267178658709854</v>
       </c>
     </row>
     <row r="21">
@@ -1702,37 +1690,37 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1002370551832925</v>
+        <v>-0.100493779719474</v>
       </c>
       <c r="H21" t="n">
-        <v>0.03116288153627861</v>
+        <v>0.03129024919719758</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00144741232738177</v>
+        <v>0.001471376924951251</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3326406718342373</v>
+        <v>-0.3318491761467815</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06505557723090659</v>
+        <v>0.06525408652065552</v>
       </c>
       <c r="L21" t="n">
-        <v>5.833213452266506e-07</v>
+        <v>6.669325665065173e-07</v>
       </c>
       <c r="M21" t="n">
-        <v>3.318539947387459</v>
+        <v>3.302186235537469</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2324036166509448</v>
+        <v>-0.2313553964273075</v>
       </c>
       <c r="O21" t="n">
-        <v>6.106951778406255e-05</v>
+        <v>6.878723115844032e-05</v>
       </c>
       <c r="P21" t="n">
         <v>330</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1452624901802011</v>
+        <v>0.1446679032843116</v>
       </c>
     </row>
     <row r="22">
@@ -1763,37 +1751,37 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.06374522592525074</v>
+        <v>-0.06408860206509255</v>
       </c>
       <c r="H22" t="n">
-        <v>0.04105175574720292</v>
+        <v>0.0411424780089641</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1215881434116413</v>
+        <v>0.1204163903820734</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3269767619804744</v>
+        <v>-0.3260819020390516</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07217673465328069</v>
+        <v>0.07235142320251069</v>
       </c>
       <c r="L22" t="n">
-        <v>8.697206201446761e-06</v>
+        <v>9.637156548336634e-06</v>
       </c>
       <c r="M22" t="n">
-        <v>5.129431376773151</v>
+        <v>5.087985874740435</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2632315360552237</v>
+        <v>-0.261993299973959</v>
       </c>
       <c r="O22" t="n">
-        <v>1.324441390937459e-05</v>
+        <v>1.520791352027651e-05</v>
       </c>
       <c r="P22" t="n">
         <v>330</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1612008359371446</v>
+        <v>0.1606133069364724</v>
       </c>
     </row>
     <row r="23">
@@ -1824,37 +1812,37 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.1287922064658172</v>
+        <v>-0.1145487920754653</v>
       </c>
       <c r="H23" t="n">
-        <v>0.03706833656549207</v>
+        <v>0.03892320622919695</v>
       </c>
       <c r="I23" t="n">
-        <v>0.000592396374449411</v>
+        <v>0.003521331839837272</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3659556768451703</v>
+        <v>-0.3557582710372422</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06111544281429826</v>
+        <v>0.05824806714099515</v>
       </c>
       <c r="L23" t="n">
-        <v>6.452330447714871e-09</v>
+        <v>3.343690213597483e-09</v>
       </c>
       <c r="M23" t="n">
-        <v>2.841442715264752</v>
+        <v>3.105735683383435</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.237163470379353</v>
+        <v>-0.2412094789617769</v>
       </c>
       <c r="O23" t="n">
-        <v>1.770157605163192e-06</v>
+        <v>6.056406531840253e-08</v>
       </c>
       <c r="P23" t="n">
         <v>330</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1627740651101907</v>
+        <v>0.1445398566896631</v>
       </c>
     </row>
     <row r="24">
@@ -1885,37 +1873,37 @@
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.0897320517321931</v>
+        <v>-0.09003656502794857</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02959464306976581</v>
+        <v>0.02974944517701831</v>
       </c>
       <c r="I24" t="n">
-        <v>0.00265416523627704</v>
+        <v>0.002701724002770467</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3450144321812073</v>
+        <v>-0.3443309326787943</v>
       </c>
       <c r="K24" t="n">
-        <v>0.06535657482373765</v>
+        <v>0.0655432944435414</v>
       </c>
       <c r="L24" t="n">
-        <v>2.591207588498179e-07</v>
+        <v>2.939900676235396e-07</v>
       </c>
       <c r="M24" t="n">
-        <v>3.844940860272637</v>
+        <v>3.824345504206089</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2552823804490142</v>
+        <v>-0.2542943676508457</v>
       </c>
       <c r="O24" t="n">
-        <v>1.666697531321759e-05</v>
+        <v>1.869014153443871e-05</v>
       </c>
       <c r="P24" t="n">
         <v>330</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1642160490175643</v>
+        <v>0.1637557644885959</v>
       </c>
     </row>
     <row r="25">
@@ -1946,37 +1934,37 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.09385694148285817</v>
+        <v>-0.09419141920294817</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0292860765231027</v>
+        <v>0.02943772867843988</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001504932727253827</v>
+        <v>0.001531109329010016</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3487983412649749</v>
+        <v>-0.3479835236224131</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0648112372947217</v>
+        <v>0.06498291859975892</v>
       </c>
       <c r="L25" t="n">
-        <v>1.541719032438493e-07</v>
+        <v>1.763993211501003e-07</v>
       </c>
       <c r="M25" t="n">
-        <v>3.716276449607925</v>
+        <v>3.694429137675859</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.2549413997821168</v>
+        <v>-0.253792104419465</v>
       </c>
       <c r="O25" t="n">
-        <v>1.470149578186586e-05</v>
+        <v>1.663275101559947e-05</v>
       </c>
       <c r="P25" t="n">
         <v>330</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1391724852863737</v>
+        <v>0.1386487859675655</v>
       </c>
     </row>
   </sheetData>

--- a/results/regression_output/pre_covid_analysis/price_robustness_matrix.xlsx
+++ b/results/regression_output/pre_covid_analysis/price_robustness_matrix.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>r_squared</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>df_resid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -543,10 +548,10 @@
         <v>-0.5950760110920712</v>
       </c>
       <c r="K2" t="n">
-        <v>0.07595852059371849</v>
+        <v>0.06080434296142236</v>
       </c>
       <c r="L2" t="n">
-        <v>1.023625628704394e-13</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>5.875861676235409</v>
@@ -562,6 +567,9 @@
       </c>
       <c r="Q2" t="n">
         <v>0.403069015694194</v>
+      </c>
+      <c r="R2" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="3">
@@ -604,10 +612,10 @@
         <v>-0.5701733674122083</v>
       </c>
       <c r="K3" t="n">
-        <v>0.08462373399190269</v>
+        <v>0.07424701915835026</v>
       </c>
       <c r="L3" t="n">
-        <v>9.086242869216221e-11</v>
+        <v>2.664535259100376e-13</v>
       </c>
       <c r="M3" t="n">
         <v>5.628074446509719</v>
@@ -623,6 +631,9 @@
       </c>
       <c r="Q3" t="n">
         <v>0.3637789415331618</v>
+      </c>
+      <c r="R3" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -665,10 +676,10 @@
         <v>-0.6184671711737429</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06144700679653801</v>
+        <v>0.07501155395072434</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>6.217248937900877e-15</v>
       </c>
       <c r="M4" t="n">
         <v>4.346337891007943</v>
@@ -684,6 +695,9 @@
       </c>
       <c r="Q4" t="n">
         <v>0.3369701883695086</v>
+      </c>
+      <c r="R4" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -726,10 +740,10 @@
         <v>-0.6038543099674142</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08660433020564759</v>
+        <v>0.07341976961093853</v>
       </c>
       <c r="L5" t="n">
-        <v>2.18360884929325e-11</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="M5" t="n">
         <v>6.740435175757209</v>
@@ -745,6 +759,9 @@
       </c>
       <c r="Q5" t="n">
         <v>0.2774644207172029</v>
+      </c>
+      <c r="R5" t="n">
+        <v>284</v>
       </c>
     </row>
     <row r="6">
@@ -787,10 +804,10 @@
         <v>-0.5960227390393019</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1165329424726069</v>
+        <v>0.07467185297924157</v>
       </c>
       <c r="L6" t="n">
-        <v>5.804106248952223e-07</v>
+        <v>3.61932706027801e-14</v>
       </c>
       <c r="M6" t="n">
         <v>17.93222435717665</v>
@@ -806,6 +823,9 @@
       </c>
       <c r="Q6" t="n">
         <v>0.2955499435836599</v>
+      </c>
+      <c r="R6" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="7">
@@ -848,10 +868,10 @@
         <v>-0.6214122143746015</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0593553884283942</v>
+        <v>0.07197738454306017</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="M7" t="n">
         <v>5.96342165976107</v>
@@ -867,6 +887,9 @@
       </c>
       <c r="Q7" t="n">
         <v>0.2770951802582408</v>
+      </c>
+      <c r="R7" t="n">
+        <v>282</v>
       </c>
     </row>
     <row r="8">
@@ -909,7 +932,7 @@
         <v>-0.6308449359973219</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0656358092886765</v>
+        <v>0.05661657363507576</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -928,6 +951,9 @@
       </c>
       <c r="Q8" t="n">
         <v>0.3009180083040703</v>
+      </c>
+      <c r="R8" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="9">
@@ -970,10 +996,10 @@
         <v>-0.6150393409074353</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08619240858568283</v>
+        <v>0.07511976413699162</v>
       </c>
       <c r="L9" t="n">
-        <v>7.997380535584853e-12</v>
+        <v>9.103828801926284e-15</v>
       </c>
       <c r="M9" t="n">
         <v>7.505932132300889</v>
@@ -989,6 +1015,9 @@
       </c>
       <c r="Q9" t="n">
         <v>0.2740896489927416</v>
+      </c>
+      <c r="R9" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -1031,10 +1060,10 @@
         <v>-0.201125537531641</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1190180056772252</v>
+        <v>0.1161171145267173</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09218102626198599</v>
+        <v>0.08437439088544485</v>
       </c>
       <c r="M10" t="n">
         <v>2.313669936192969</v>
@@ -1050,6 +1079,9 @@
       </c>
       <c r="Q10" t="n">
         <v>0.2249862438760502</v>
+      </c>
+      <c r="R10" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="11">
@@ -1092,10 +1124,10 @@
         <v>-0.2112470180884315</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1060068296409136</v>
+        <v>0.1078357903277823</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04725394141242312</v>
+        <v>0.05110512969567083</v>
       </c>
       <c r="M11" t="n">
         <v>2.302134686022447</v>
@@ -1111,6 +1143,9 @@
       </c>
       <c r="Q11" t="n">
         <v>0.1905718733684744</v>
+      </c>
+      <c r="R11" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="12">
@@ -1153,10 +1188,10 @@
         <v>-0.2444837981111417</v>
       </c>
       <c r="K12" t="n">
-        <v>0.09612199239963096</v>
+        <v>0.1056747903272247</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01150786283431304</v>
+        <v>0.02140915024815215</v>
       </c>
       <c r="M12" t="n">
         <v>1.954381118190802</v>
@@ -1172,6 +1207,9 @@
       </c>
       <c r="Q12" t="n">
         <v>0.1285444921606054</v>
+      </c>
+      <c r="R12" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="13">
@@ -1214,10 +1252,10 @@
         <v>-0.1637673583693385</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1096521600333624</v>
+        <v>0.1132597743201852</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1364120607850898</v>
+        <v>0.1492953796266616</v>
       </c>
       <c r="M13" t="n">
         <v>1.41619154291951</v>
@@ -1233,6 +1271,9 @@
       </c>
       <c r="Q13" t="n">
         <v>0.0708976237478558</v>
+      </c>
+      <c r="R13" t="n">
+        <v>284</v>
       </c>
     </row>
     <row r="14">
@@ -1275,10 +1316,10 @@
         <v>-0.1545044948142994</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1177796018541008</v>
+        <v>0.1091132915538867</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1906472892557163</v>
+        <v>0.1578749574063827</v>
       </c>
       <c r="M14" t="n">
         <v>1.905728432252884</v>
@@ -1294,6 +1335,9 @@
       </c>
       <c r="Q14" t="n">
         <v>0.09100306375979428</v>
+      </c>
+      <c r="R14" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="15">
@@ -1336,10 +1380,10 @@
         <v>-0.1796818489793458</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1017675759472893</v>
+        <v>0.1124902433987762</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07854343140638864</v>
+        <v>0.1113164113801686</v>
       </c>
       <c r="M15" t="n">
         <v>1.465878007817337</v>
@@ -1355,6 +1399,9 @@
       </c>
       <c r="Q15" t="n">
         <v>0.05880099894762103</v>
+      </c>
+      <c r="R15" t="n">
+        <v>282</v>
       </c>
     </row>
     <row r="16">
@@ -1397,10 +1444,10 @@
         <v>-0.167551056442428</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1243667158363113</v>
+        <v>0.1241014862597481</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1789826141686581</v>
+        <v>0.178058461638368</v>
       </c>
       <c r="M16" t="n">
         <v>1.613428463581538</v>
@@ -1416,6 +1463,9 @@
       </c>
       <c r="Q16" t="n">
         <v>0.08114530466849679</v>
+      </c>
+      <c r="R16" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="17">
@@ -1458,10 +1508,10 @@
         <v>-0.1774597409034677</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1068376800558504</v>
+        <v>0.1114159549912183</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09780866572558899</v>
+        <v>0.1123207503210644</v>
       </c>
       <c r="M17" t="n">
         <v>1.585481638194635</v>
@@ -1477,6 +1527,9 @@
       </c>
       <c r="Q17" t="n">
         <v>0.05400941519282243</v>
+      </c>
+      <c r="R17" t="n">
+        <v>285</v>
       </c>
     </row>
     <row r="18">
@@ -1519,10 +1572,10 @@
         <v>-0.3396844116817059</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06702015540221941</v>
+        <v>0.05932461705441426</v>
       </c>
       <c r="L18" t="n">
-        <v>7.360549447721354e-07</v>
+        <v>2.682891353522621e-08</v>
       </c>
       <c r="M18" t="n">
         <v>3.480225230324073</v>
@@ -1538,6 +1591,9 @@
       </c>
       <c r="Q18" t="n">
         <v>0.2921014599829125</v>
+      </c>
+      <c r="R18" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="19">
@@ -1580,10 +1636,10 @@
         <v>-0.3374395463820286</v>
       </c>
       <c r="K19" t="n">
-        <v>0.06013286971239342</v>
+        <v>0.06321790234082855</v>
       </c>
       <c r="L19" t="n">
-        <v>4.803991071611335e-08</v>
+        <v>1.942221532491573e-07</v>
       </c>
       <c r="M19" t="n">
         <v>3.425110792466736</v>
@@ -1599,6 +1655,9 @@
       </c>
       <c r="Q19" t="n">
         <v>0.2579319977482214</v>
+      </c>
+      <c r="R19" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="20">
@@ -1641,10 +1700,10 @@
         <v>-0.3899023745975941</v>
       </c>
       <c r="K20" t="n">
-        <v>0.05606709710336186</v>
+        <v>0.06290169541157964</v>
       </c>
       <c r="L20" t="n">
-        <v>2.455791126010354e-11</v>
+        <v>2.008120114638245e-09</v>
       </c>
       <c r="M20" t="n">
         <v>3.146929888093275</v>
@@ -1660,6 +1719,9 @@
       </c>
       <c r="Q20" t="n">
         <v>0.2267178658709854</v>
+      </c>
+      <c r="R20" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="21">
@@ -1702,10 +1764,10 @@
         <v>-0.3318491761467815</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06525408652065552</v>
+        <v>0.06480240575412406</v>
       </c>
       <c r="L21" t="n">
-        <v>6.669325665065173e-07</v>
+        <v>5.617630505216908e-07</v>
       </c>
       <c r="M21" t="n">
         <v>3.302186235537469</v>
@@ -1721,6 +1783,9 @@
       </c>
       <c r="Q21" t="n">
         <v>0.1446679032843116</v>
+      </c>
+      <c r="R21" t="n">
+        <v>284</v>
       </c>
     </row>
     <row r="22">
@@ -1763,10 +1828,10 @@
         <v>-0.3260819020390516</v>
       </c>
       <c r="K22" t="n">
-        <v>0.07235142320251069</v>
+        <v>0.05935203360897374</v>
       </c>
       <c r="L22" t="n">
-        <v>9.637156548336634e-06</v>
+        <v>8.75922931964368e-08</v>
       </c>
       <c r="M22" t="n">
         <v>5.087985874740435</v>
@@ -1782,6 +1847,9 @@
       </c>
       <c r="Q22" t="n">
         <v>0.1606133069364724</v>
+      </c>
+      <c r="R22" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="23">
@@ -1824,10 +1892,10 @@
         <v>-0.3557582710372422</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05824806714099515</v>
+        <v>0.06282313831245995</v>
       </c>
       <c r="L23" t="n">
-        <v>3.343690213597483e-09</v>
+        <v>3.665752279502499e-08</v>
       </c>
       <c r="M23" t="n">
         <v>3.105735683383435</v>
@@ -1843,6 +1911,9 @@
       </c>
       <c r="Q23" t="n">
         <v>0.1445398566896631</v>
+      </c>
+      <c r="R23" t="n">
+        <v>282</v>
       </c>
     </row>
     <row r="24">
@@ -1885,10 +1956,10 @@
         <v>-0.3443309326787943</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0655432944435414</v>
+        <v>0.06111307226734932</v>
       </c>
       <c r="L24" t="n">
-        <v>2.939900676235396e-07</v>
+        <v>4.24249113617492e-08</v>
       </c>
       <c r="M24" t="n">
         <v>3.824345504206089</v>
@@ -1904,6 +1975,9 @@
       </c>
       <c r="Q24" t="n">
         <v>0.1637557644885959</v>
+      </c>
+      <c r="R24" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="25">
@@ -1946,10 +2020,10 @@
         <v>-0.3479835236224131</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06498291859975892</v>
+        <v>0.06563250871679666</v>
       </c>
       <c r="L25" t="n">
-        <v>1.763993211501003e-07</v>
+        <v>2.2998719928502e-07</v>
       </c>
       <c r="M25" t="n">
         <v>3.694429137675859</v>
@@ -1965,6 +2039,9 @@
       </c>
       <c r="Q25" t="n">
         <v>0.1386487859675655</v>
+      </c>
+      <c r="R25" t="n">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
